--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_antofagasta.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:08</t>
+    <t xml:space="preserve">2026-09-24 00:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -639,10 +639,10 @@
         <v>0.74</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="6">
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="9">
@@ -731,10 +731,10 @@
         <v>-0.03</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="10">
@@ -771,7 +771,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="G11" s="2"/>
     </row>
@@ -792,7 +792,7 @@
         <v>0.09</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.01</v>
@@ -861,10 +861,10 @@
         <v>-0.29</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="16">
@@ -887,7 +887,7 @@
         <v>-0.42</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -907,10 +907,10 @@
         <v>-0.49</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="18">
@@ -953,10 +953,10 @@
         <v>0.58</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="20">
@@ -976,10 +976,10 @@
         <v>0.87</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="21">
@@ -1071,7 +1071,7 @@
         <v>-0.2</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="25">
@@ -1186,7 +1186,7 @@
         <v>-0.08</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="30">
@@ -1316,7 +1316,7 @@
         <v>-0.06</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="36">
@@ -1405,10 +1405,10 @@
         <v>-0.68</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>-1.05</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="40">
@@ -1428,10 +1428,10 @@
         <v>-0.51</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="41">
@@ -1857,10 +1857,10 @@
         <v>0.81</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="60">
@@ -1880,10 +1880,10 @@
         <v>0.54</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="61">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_antofagasta.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:59</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_antofagasta.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-05 19:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
